--- a/artfynd/A 10960-2025 artfynd.xlsx
+++ b/artfynd/A 10960-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123515285</v>
+        <v>123515276</v>
       </c>
       <c r="B2" t="n">
-        <v>92244</v>
+        <v>95043</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548203</v>
+        <v>548383</v>
       </c>
       <c r="R2" t="n">
-        <v>6515774</v>
+        <v>6516083</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>02:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>02:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>123515281</v>
       </c>
       <c r="B3" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123515276</v>
+        <v>123515275</v>
       </c>
       <c r="B4" t="n">
-        <v>95040</v>
+        <v>95043</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548383</v>
+        <v>548436</v>
       </c>
       <c r="R4" t="n">
-        <v>6516083</v>
+        <v>6516041</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>02:01</t>
+          <t>02:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>02:01</t>
+          <t>02:14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gammal stubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123515275</v>
+        <v>123515284</v>
       </c>
       <c r="B5" t="n">
-        <v>95040</v>
+        <v>94996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1032,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Peterslund, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548436</v>
+        <v>548110</v>
       </c>
       <c r="R5" t="n">
-        <v>6516041</v>
+        <v>6515844</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1086,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>02:14</t>
+          <t>01:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>02:14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gammal stubbe</t>
+          <t>01:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123515284</v>
+        <v>123515285</v>
       </c>
       <c r="B6" t="n">
-        <v>94993</v>
+        <v>92247</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,38 +1148,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Peterslund, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548110</v>
+        <v>548203</v>
       </c>
       <c r="R6" t="n">
-        <v>6515844</v>
+        <v>6515774</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>01:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>01:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,7 +1247,7 @@
         <v>123515286</v>
       </c>
       <c r="B7" t="n">
-        <v>94993</v>
+        <v>94996</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 10960-2025 artfynd.xlsx
+++ b/artfynd/A 10960-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123515276</v>
+        <v>123515284</v>
       </c>
       <c r="B2" t="n">
-        <v>95043</v>
+        <v>95013</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Peterslund, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548383</v>
+        <v>548110</v>
       </c>
       <c r="R2" t="n">
-        <v>6516083</v>
+        <v>6515844</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>02:01</t>
+          <t>01:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>02:01</t>
+          <t>01:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123515281</v>
+        <v>123515285</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>92264</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548289</v>
+        <v>548203</v>
       </c>
       <c r="R3" t="n">
-        <v>6516093</v>
+        <v>6515774</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>01:46</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>01:46</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123515275</v>
+        <v>123515281</v>
       </c>
       <c r="B4" t="n">
-        <v>95043</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548436</v>
+        <v>548289</v>
       </c>
       <c r="R4" t="n">
-        <v>6516041</v>
+        <v>6516093</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>02:14</t>
+          <t>01:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>02:14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gammal stubbe</t>
+          <t>01:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123515284</v>
+        <v>123515286</v>
       </c>
       <c r="B5" t="n">
-        <v>94996</v>
+        <v>95013</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,7 +1050,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1060,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548110</v>
+        <v>548185</v>
       </c>
       <c r="R5" t="n">
-        <v>6515844</v>
+        <v>6515804</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1095,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>01:04</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>01:04</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,6 +1115,14 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1132,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123515285</v>
+        <v>123515276</v>
       </c>
       <c r="B6" t="n">
-        <v>92247</v>
+        <v>95060</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548203</v>
+        <v>548383</v>
       </c>
       <c r="R6" t="n">
-        <v>6515774</v>
+        <v>6516083</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1207,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>02:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1224,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>02:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123515286</v>
+        <v>123515275</v>
       </c>
       <c r="B7" t="n">
-        <v>94996</v>
+        <v>95060</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,38 +1267,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Peterslund, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548185</v>
+        <v>548436</v>
       </c>
       <c r="R7" t="n">
-        <v>6515804</v>
+        <v>6516041</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1323,7 +1326,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>02:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1336,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>02:14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gammal stubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,14 +1352,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 10960-2025 artfynd.xlsx
+++ b/artfynd/A 10960-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123515284</v>
       </c>
       <c r="B2" t="n">
-        <v>95013</v>
+        <v>95019</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>123515285</v>
       </c>
       <c r="B3" t="n">
-        <v>92264</v>
+        <v>92269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123515281</v>
+        <v>123515276</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
+        <v>95066</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +915,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548289</v>
+        <v>548383</v>
       </c>
       <c r="R4" t="n">
-        <v>6516093</v>
+        <v>6516083</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>01:46</t>
+          <t>02:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>01:46</t>
+          <t>02:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123515286</v>
+        <v>123515281</v>
       </c>
       <c r="B5" t="n">
-        <v>95013</v>
+        <v>78786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,42 +1027,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Peterslund, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548185</v>
+        <v>548289</v>
       </c>
       <c r="R5" t="n">
-        <v>6515804</v>
+        <v>6516093</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1094,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>01:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>01:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,14 +1111,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1139,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123515276</v>
+        <v>123515275</v>
       </c>
       <c r="B6" t="n">
-        <v>95060</v>
+        <v>95066</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548383</v>
+        <v>548436</v>
       </c>
       <c r="R6" t="n">
-        <v>6516083</v>
+        <v>6516041</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1214,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>02:01</t>
+          <t>02:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,7 +1212,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>02:01</t>
+          <t>02:14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammal stubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123515275</v>
+        <v>123515286</v>
       </c>
       <c r="B7" t="n">
-        <v>95060</v>
+        <v>95019</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,34 +1260,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Peterslund, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548436</v>
+        <v>548185</v>
       </c>
       <c r="R7" t="n">
-        <v>6516041</v>
+        <v>6515804</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1326,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>02:14</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1336,12 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>02:14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gammal stubbe</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,6 +1344,14 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 10960-2025 artfynd.xlsx
+++ b/artfynd/A 10960-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123515284</v>
+        <v>123515285</v>
       </c>
       <c r="B2" t="n">
-        <v>95019</v>
+        <v>92271</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Peterslund, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548110</v>
+        <v>548203</v>
       </c>
       <c r="R2" t="n">
-        <v>6515844</v>
+        <v>6515774</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>01:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>01:04</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123515285</v>
+        <v>123515286</v>
       </c>
       <c r="B3" t="n">
-        <v>92269</v>
+        <v>95021</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,34 +803,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Peterslund, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548203</v>
+        <v>548185</v>
       </c>
       <c r="R3" t="n">
-        <v>6515774</v>
+        <v>6515804</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,6 +887,14 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -906,7 +914,7 @@
         <v>123515276</v>
       </c>
       <c r="B4" t="n">
-        <v>95066</v>
+        <v>95068</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1015,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123515281</v>
+        <v>123515284</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>95021</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,38 +1035,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Peterslund, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548289</v>
+        <v>548110</v>
       </c>
       <c r="R5" t="n">
-        <v>6516093</v>
+        <v>6515844</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1090,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>01:46</t>
+          <t>01:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>01:46</t>
+          <t>01:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123515275</v>
+        <v>123515281</v>
       </c>
       <c r="B6" t="n">
-        <v>95066</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,25 +1151,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548436</v>
+        <v>548289</v>
       </c>
       <c r="R6" t="n">
-        <v>6516041</v>
+        <v>6516093</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1202,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>02:14</t>
+          <t>01:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,12 +1224,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>02:14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammal stubbe</t>
+          <t>01:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123515286</v>
+        <v>123515275</v>
       </c>
       <c r="B7" t="n">
-        <v>95019</v>
+        <v>95068</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,38 +1267,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Peterslund, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548185</v>
+        <v>548436</v>
       </c>
       <c r="R7" t="n">
-        <v>6515804</v>
+        <v>6516041</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1323,7 +1326,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>02:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1336,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>02:14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gammal stubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,14 +1352,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 10960-2025 artfynd.xlsx
+++ b/artfynd/A 10960-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123515286</v>
+        <v>123515284</v>
       </c>
       <c r="B3" t="n">
-        <v>95021</v>
+        <v>95529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548185</v>
+        <v>548110</v>
       </c>
       <c r="R3" t="n">
-        <v>6515804</v>
+        <v>6515844</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>01:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>01:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,14 +887,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,7 +906,7 @@
         <v>123515276</v>
       </c>
       <c r="B4" t="n">
-        <v>95068</v>
+        <v>95576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1023,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123515284</v>
+        <v>123515286</v>
       </c>
       <c r="B5" t="n">
-        <v>95021</v>
+        <v>95529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,7 +1050,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1067,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548110</v>
+        <v>548185</v>
       </c>
       <c r="R5" t="n">
-        <v>6515844</v>
+        <v>6515804</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1102,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>01:04</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>01:04</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,6 +1115,14 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123515281</v>
+        <v>123515275</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>95576</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,25 +1151,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548289</v>
+        <v>548436</v>
       </c>
       <c r="R6" t="n">
-        <v>6516093</v>
+        <v>6516041</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>01:46</t>
+          <t>02:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,7 +1224,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>01:46</t>
+          <t>02:14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammal stubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123515275</v>
+        <v>123515281</v>
       </c>
       <c r="B7" t="n">
-        <v>95068</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,25 +1268,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1291,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548436</v>
+        <v>548289</v>
       </c>
       <c r="R7" t="n">
-        <v>6516041</v>
+        <v>6516093</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1326,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>02:14</t>
+          <t>01:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1336,12 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>02:14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gammal stubbe</t>
+          <t>01:46</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 10960-2025 artfynd.xlsx
+++ b/artfynd/A 10960-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123515285</v>
+        <v>123515275</v>
       </c>
       <c r="B2" t="n">
-        <v>92271</v>
+        <v>95576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548203</v>
+        <v>548436</v>
       </c>
       <c r="R2" t="n">
-        <v>6515774</v>
+        <v>6516041</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>02:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>02:14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gammal stubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1015,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123515286</v>
+        <v>123515285</v>
       </c>
       <c r="B5" t="n">
-        <v>95529</v>
+        <v>92271</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,38 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Peterslund, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548185</v>
+        <v>548203</v>
       </c>
       <c r="R5" t="n">
-        <v>6515804</v>
+        <v>6515774</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1094,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,14 +1116,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1139,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123515275</v>
+        <v>123515281</v>
       </c>
       <c r="B6" t="n">
-        <v>95576</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,25 +1144,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548436</v>
+        <v>548289</v>
       </c>
       <c r="R6" t="n">
-        <v>6516041</v>
+        <v>6516093</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1214,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>02:14</t>
+          <t>01:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,12 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>02:14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammal stubbe</t>
+          <t>01:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123515281</v>
+        <v>123515286</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>95529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,38 +1256,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Peterslund, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548289</v>
+        <v>548185</v>
       </c>
       <c r="R7" t="n">
-        <v>6516093</v>
+        <v>6515804</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1331,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>01:46</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>01:46</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,6 +1344,14 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 10960-2025 artfynd.xlsx
+++ b/artfynd/A 10960-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123515275</v>
+        <v>123515276</v>
       </c>
       <c r="B2" t="n">
         <v>95576</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548436</v>
+        <v>548383</v>
       </c>
       <c r="R2" t="n">
-        <v>6516041</v>
+        <v>6516083</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>02:14</t>
+          <t>02:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>02:14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gammal stubbe</t>
+          <t>02:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -908,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123515276</v>
+        <v>123515285</v>
       </c>
       <c r="B4" t="n">
-        <v>95576</v>
+        <v>92271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548383</v>
+        <v>548203</v>
       </c>
       <c r="R4" t="n">
-        <v>6516083</v>
+        <v>6515774</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -983,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>02:01</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>02:01</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123515285</v>
+        <v>123515275</v>
       </c>
       <c r="B5" t="n">
-        <v>92271</v>
+        <v>95576</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548203</v>
+        <v>548436</v>
       </c>
       <c r="R5" t="n">
-        <v>6515774</v>
+        <v>6516041</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1095,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>02:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>02:14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gammal stubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 10960-2025 artfynd.xlsx
+++ b/artfynd/A 10960-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123515276</v>
+        <v>123515284</v>
       </c>
       <c r="B2" t="n">
-        <v>95576</v>
+        <v>95529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Peterslund, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548383</v>
+        <v>548110</v>
       </c>
       <c r="R2" t="n">
-        <v>6516083</v>
+        <v>6515844</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>02:01</t>
+          <t>01:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>02:01</t>
+          <t>01:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123515284</v>
+        <v>123515281</v>
       </c>
       <c r="B3" t="n">
-        <v>95529</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +803,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Peterslund, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548110</v>
+        <v>548289</v>
       </c>
       <c r="R3" t="n">
-        <v>6515844</v>
+        <v>6516093</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>01:04</t>
+          <t>01:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>01:04</t>
+          <t>01:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1015,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123515275</v>
+        <v>123515276</v>
       </c>
       <c r="B5" t="n">
         <v>95576</v>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548436</v>
+        <v>548383</v>
       </c>
       <c r="R5" t="n">
-        <v>6516041</v>
+        <v>6516083</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>02:14</t>
+          <t>02:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>02:14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gammal stubbe</t>
+          <t>02:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123515281</v>
+        <v>123515275</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>95576</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,25 +1139,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548289</v>
+        <v>548436</v>
       </c>
       <c r="R6" t="n">
-        <v>6516093</v>
+        <v>6516041</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1207,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>01:46</t>
+          <t>02:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1212,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>01:46</t>
+          <t>02:14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammal stubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 10960-2025 artfynd.xlsx
+++ b/artfynd/A 10960-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123515284</v>
+        <v>123515275</v>
       </c>
       <c r="B2" t="n">
-        <v>95529</v>
+        <v>95576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Peterslund, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548110</v>
+        <v>548436</v>
       </c>
       <c r="R2" t="n">
-        <v>6515844</v>
+        <v>6516041</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>01:04</t>
+          <t>02:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>01:04</t>
+          <t>02:14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gammal stubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123515281</v>
+        <v>123515284</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>95529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +804,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Peterslund, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548289</v>
+        <v>548110</v>
       </c>
       <c r="R3" t="n">
-        <v>6516093</v>
+        <v>6515844</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -866,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>01:46</t>
+          <t>01:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>01:46</t>
+          <t>01:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123515285</v>
+        <v>123515286</v>
       </c>
       <c r="B4" t="n">
-        <v>92271</v>
+        <v>95529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,34 +924,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Peterslund, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548203</v>
+        <v>548185</v>
       </c>
       <c r="R4" t="n">
-        <v>6515774</v>
+        <v>6515804</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -978,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,6 +1008,14 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1015,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123515276</v>
+        <v>123515281</v>
       </c>
       <c r="B5" t="n">
-        <v>95576</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,25 +1044,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548383</v>
+        <v>548289</v>
       </c>
       <c r="R5" t="n">
-        <v>6516083</v>
+        <v>6516093</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1090,7 +1107,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>02:01</t>
+          <t>01:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1117,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>02:01</t>
+          <t>01:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123515275</v>
+        <v>123515285</v>
       </c>
       <c r="B6" t="n">
-        <v>95576</v>
+        <v>92271</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1160,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548436</v>
+        <v>548203</v>
       </c>
       <c r="R6" t="n">
-        <v>6516041</v>
+        <v>6515774</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1202,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>02:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,12 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>02:14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammal stubbe</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123515286</v>
+        <v>123515276</v>
       </c>
       <c r="B7" t="n">
-        <v>95529</v>
+        <v>95576</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,38 +1272,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Peterslund, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548185</v>
+        <v>548383</v>
       </c>
       <c r="R7" t="n">
-        <v>6515804</v>
+        <v>6516083</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1323,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>02:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>02:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,14 +1352,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>1 substratenheter</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
